--- a/sheets/민요/검수/제주도 타령 닐리리야.xlsx
+++ b/sheets/민요/검수/제주도 타령 닐리리야.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4136,8 +4252,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4156,1085 +4276,1059 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제주도 타령 닐리리야 — 민요채보-2/제주도 타령 닐리리야.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">제주도 타령 닐리리야</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 夾</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">낫</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 夾</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 夾</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="16"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="16"/>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 夾</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">녁</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 夾</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">침</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="18"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M5" s="18"/>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O5" s="18"/>
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 夾</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="C6" s="15"/>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 夾</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 夾</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 夾</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 夾</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 夾</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="G8" s="18"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 夾</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 夾</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="Q8" s="18"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">돌</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="15"/>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 夾</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">배</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="16"/>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I10" s="16"/>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 夾</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="Q10" s="16"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="18"/>
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 夾</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 夾</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 夾</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="15"/>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="15"/>
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="15"/>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">참</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 夾</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="P13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="18"/>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="18"/>
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="18"/>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/제주도 타령 닐리리야.xlsx
+++ b/sheets/민요/검수/제주도 타령 닐리리야.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|湳</t>
+          <t xml:space="preserve">–|湳</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I75" s="2"/>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3995,7 +3995,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="9"/>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="10"/>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="9"/>
@@ -4691,20 +4691,20 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -4758,7 +4758,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4781,7 +4781,7 @@
       <c r="I14" s="10"/>
       <c r="J14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="N14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/제주도 타령 닐리리야.xlsx
+++ b/sheets/민요/검수/제주도 타령 닐리리야.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3890,102 +3931,102 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">제주도 타령 / 닐리리야</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 湳</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="H3" s="21"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">낮에</t>
         </is>
       </c>
-      <c r="L3" s="18" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3993,71 +4034,71 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="H4" s="21"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">낮에</t>
         </is>
       </c>
-      <c r="L4" s="18" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">녁</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">침</t>
         </is>
@@ -4065,73 +4106,73 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="H5" s="21"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="27"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4139,80 +4180,80 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">밤에</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우는</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우는</t>
         </is>
@@ -4220,72 +4261,72 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="G7" s="25"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">밤에</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4293,75 +4334,75 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 無</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="G8" s="27"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">냐</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4369,80 +4410,80 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내가</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">참사</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㴌</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">두리</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님이</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">배가</t>
         </is>
@@ -4450,82 +4491,82 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">돌아</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="H10" s="21"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">랑이</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">그리</t>
         </is>
       </c>
-      <c r="P10" s="18" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q10" s="12" t="inlineStr">
+      <c r="Q10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4533,80 +4574,80 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="H11" s="21"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">파</t>
         </is>
@@ -4614,74 +4655,74 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="N12" s="18" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -4689,66 +4730,66 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 㴌</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="Q13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4756,60 +4797,60 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="28"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌
 △</t>
         </is>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="G14" s="28"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="28"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="28"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>

--- a/sheets/민요/검수/제주도 타령 닐리리야.xlsx
+++ b/sheets/민요/검수/제주도 타령 닐리리야.xlsx
@@ -3908,28 +3908,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4764,38 +4764,38 @@
       </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-㴌</t>
-        </is>
-      </c>
-      <c r="M13" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
-        </is>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南^</t>
-        </is>
-      </c>
-      <c r="O13" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="O13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+㴌</t>
+        </is>
+      </c>
       <c r="Q13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>

--- a/sheets/민요/검수/제주도 타령 닐리리야.xlsx
+++ b/sheets/민요/검수/제주도 타령 닐리리야.xlsx
@@ -3995,7 +3995,8 @@
       </c>
       <c r="K3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">낮에</t>
+          <t xml:space="preserve">낮
+에</t>
         </is>
       </c>
       <c r="L3" s="23" t="inlineStr">
@@ -4070,7 +4071,8 @@
       </c>
       <c r="K4" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">낮에</t>
+          <t xml:space="preserve">낮
+에</t>
         </is>
       </c>
       <c r="L4" s="23" t="inlineStr">
@@ -4222,7 +4224,8 @@
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">밤에</t>
+          <t xml:space="preserve">밤
+에</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -4244,7 +4247,8 @@
       </c>
       <c r="O6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우는</t>
+          <t xml:space="preserve">우
+는</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
@@ -4255,7 +4259,8 @@
       </c>
       <c r="Q6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우는</t>
+          <t xml:space="preserve">우
+는</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4303,8 @@
       </c>
       <c r="K7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">밤에</t>
+          <t xml:space="preserve">밤
+에</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -4428,7 +4434,8 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">내가</t>
+          <t xml:space="preserve">내
+가</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -4452,7 +4459,8 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">참사</t>
+          <t xml:space="preserve">참
+사</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -4463,7 +4471,8 @@
       </c>
       <c r="M9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">두리</t>
+          <t xml:space="preserve">두
+리</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -4474,7 +4483,8 @@
       </c>
       <c r="O9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">님이</t>
+          <t xml:space="preserve">님
+이</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -4485,7 +4495,8 @@
       </c>
       <c r="Q9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">배가</t>
+          <t xml:space="preserve">배
+가</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4522,8 @@
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">돌아</t>
+          <t xml:space="preserve">돌
+아</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -4535,7 +4547,8 @@
       </c>
       <c r="K10" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑이</t>
+          <t xml:space="preserve">랑
+이</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -4557,7 +4570,8 @@
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">그리</t>
+          <t xml:space="preserve">그
+리</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">

--- a/sheets/민요/검수/제주도 타령 닐리리야.xlsx
+++ b/sheets/민요/검수/제주도 타령 닐리리야.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3959,7 +3982,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
@@ -3969,7 +3992,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -3980,20 +4003,20 @@
 湳</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
       <c r="H3" s="21"/>
-      <c r="I3" s="22"/>
+      <c r="I3" s="29"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">낮
 에</t>
@@ -4005,7 +4028,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4016,7 +4039,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4027,7 +4050,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4040,13 +4063,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4056,20 +4079,20 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="H4" s="21"/>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">낮
 에</t>
@@ -4080,7 +4103,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
@@ -4090,7 +4113,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">녁</t>
         </is>
@@ -4100,7 +4123,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">침</t>
         </is>
@@ -4115,7 +4138,7 @@
 南</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4126,7 +4149,7 @@
 無</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -4136,19 +4159,19 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="H5" s="21"/>
-      <c r="I5" s="27"/>
+      <c r="I5" s="33"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4158,13 +4181,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="27"/>
+      <c r="M5" s="33"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4174,7 +4197,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q5" s="27" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4188,7 +4211,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4199,7 +4222,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
@@ -4209,20 +4232,20 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
+      <c r="I6" s="29"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">밤
 에</t>
@@ -4234,7 +4257,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4245,7 +4268,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 는</t>
@@ -4257,7 +4280,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 는</t>
@@ -4271,7 +4294,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4282,7 +4305,7 @@
 無</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -4292,16 +4315,16 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="31"/>
       <c r="H7" s="21"/>
-      <c r="I7" s="25"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">밤
 에</t>
@@ -4312,7 +4335,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4322,7 +4345,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4332,7 +4355,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4347,7 +4370,7 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4357,7 +4380,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -4368,15 +4391,15 @@
 △</t>
         </is>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="21"/>
-      <c r="I8" s="27"/>
+      <c r="I8" s="33"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="27" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4387,7 +4410,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M8" s="28" t="inlineStr">
+      <c r="M8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">냐</t>
         </is>
@@ -4397,7 +4420,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="27" t="inlineStr">
+      <c r="O8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4408,7 +4431,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q8" s="27" t="inlineStr">
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4421,7 +4444,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
@@ -4432,7 +4455,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">내
 가</t>
@@ -4444,20 +4467,20 @@
 㴌</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
       <c r="H9" s="21"/>
-      <c r="I9" s="22"/>
+      <c r="I9" s="29"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">참
 사</t>
@@ -4469,7 +4492,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">두
 리</t>
@@ -4481,7 +4504,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">님
 이</t>
@@ -4493,7 +4516,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">배
 가</t>
@@ -4509,7 +4532,7 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4520,7 +4543,7 @@
 南</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">돌
 아</t>
@@ -4532,20 +4555,20 @@
 湳</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="H10" s="21"/>
-      <c r="I10" s="25"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">랑
 이</t>
@@ -4557,7 +4580,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
@@ -4568,7 +4591,7 @@
 南</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 리</t>
@@ -4580,7 +4603,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q10" s="26" t="inlineStr">
+      <c r="Q10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4595,7 +4618,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4605,7 +4628,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
@@ -4615,20 +4638,20 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="H11" s="21"/>
-      <c r="I11" s="27"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -4639,7 +4662,7 @@
 湳</t>
         </is>
       </c>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -4650,7 +4673,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O11" s="27" t="inlineStr">
+      <c r="O11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
@@ -4661,7 +4684,7 @@
 湳</t>
         </is>
       </c>
-      <c r="Q11" s="27" t="inlineStr">
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">파</t>
         </is>
@@ -4674,7 +4697,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -4684,7 +4707,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4694,19 +4717,19 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="H12" s="21"/>
-      <c r="I12" s="22"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4716,7 +4739,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
@@ -4726,7 +4749,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="O12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -4736,7 +4759,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -4749,29 +4772,29 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21"/>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4782,7 +4805,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4792,7 +4815,7 @@
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="O13" s="25" t="inlineStr">
+      <c r="O13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4803,7 +4826,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="Q13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4817,13 +4840,13 @@
 △</t>
         </is>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
@@ -4831,23 +4854,23 @@
 △</t>
         </is>
       </c>
-      <c r="G14" s="28"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K14" s="28"/>
+      <c r="K14" s="34"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △</t>
         </is>
       </c>
-      <c r="M14" s="27" t="inlineStr">
+      <c r="M14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -4858,13 +4881,13 @@
 △</t>
         </is>
       </c>
-      <c r="O14" s="28"/>
+      <c r="O14" s="34"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q14" s="27" t="inlineStr">
+      <c r="Q14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>

--- a/sheets/민요/검수/제주도 타령 닐리리야.xlsx
+++ b/sheets/민요/검수/제주도 타령 닐리리야.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,24 +236,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
@@ -389,7 +366,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상</t>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
     </row>
@@ -401,7 +378,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 장에 두 곡</t>
+          <t xml:space="preserve">비고 18%, 한 장에 두 곡</t>
         </is>
       </c>
     </row>
@@ -429,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸에 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 1~4줄이 제주도 타령. 5줄 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 6~8줄이 닐리리야. 9줄은 빈 칸. 각 율명 줄 바로 오른쪽 좁은 칸의 가사를 전사함. 줄 끝 아래 D 모양 표시는 2_제주도 타령(같은 가락)과 비교해 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변이 없는 것은 南, 있는 것은 姑로 적음. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 줄1~4 제주도 타령. 줄5 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 줄6~8 닐리리야. 맨 왼쪽 빈 줄은 #줄수에서 뺌. 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 줄 끝의 D 모양 표시는 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변 없는 것은 南, 있는 것은 姑.</t>
         </is>
       </c>
     </row>
@@ -910,7 +887,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 칸 고 아래 겹쳐 쓴 글자(파?)</t>
+          <t xml:space="preserve">가사 고 옆에 덧쓴 글자(파?)</t>
         </is>
       </c>
       <c r="K9" s="2"/>
@@ -1450,26 +1427,22 @@
       <c r="F23" s="2">
         <v>4</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南 흘림(古처럼 보임)</t>
-        </is>
-      </c>
+      <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
     <row r="24">
@@ -1546,7 +1519,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D 모양으로 흘린 △</t>
+          <t xml:space="preserve">D 모양으로 흘린 끝 표시, △로 봄</t>
         </is>
       </c>
       <c r="K25" s="2"/>
@@ -1590,7 +1563,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 비처럼도 보임</t>
+          <t xml:space="preserve">가사 ㅂ처럼 흘림</t>
         </is>
       </c>
       <c r="K26" s="2"/>
@@ -1633,7 +1606,7 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사에 동그라미</t>
+          <t xml:space="preserve">가사 난과 율명에 동그라미</t>
         </is>
       </c>
       <c r="K27" s="2"/>
@@ -1791,7 +1764,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사에 동그라미</t>
+          <t xml:space="preserve">가사 냐에 동그라미</t>
         </is>
       </c>
       <c r="K31" s="2"/>
@@ -1857,23 +1830,27 @@
       <c r="F33" s="2">
         <v>3</v>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="J33" s="4"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">윗글자 氵가 작게 붙음(㳞?)</t>
+        </is>
+      </c>
       <c r="K33" s="2"/>
     </row>
     <row r="34">
@@ -2096,27 +2073,23 @@
       <c r="F39" s="2">
         <v>1</v>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌|㴌</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">낮에</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">윗글자 淋처럼도 보임</t>
-        </is>
-      </c>
+      <c r="J39" s="4"/>
       <c r="K39" s="2"/>
     </row>
     <row r="40">
@@ -2356,7 +2329,7 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 강이처럼도 보임</t>
+          <t xml:space="preserve">가사 강이처럼 보임</t>
         </is>
       </c>
       <c r="K45" s="2"/>
@@ -2461,22 +2434,26 @@
       <c r="F48" s="2">
         <v>4</v>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J48" s="4"/>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南 흘림(古처럼, 女변 없음)</t>
+        </is>
+      </c>
       <c r="K48" s="2"/>
     </row>
     <row r="49">
@@ -2514,7 +2491,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D 모양으로 흘린 △</t>
+          <t xml:space="preserve">D 모양으로 흘린 끝 표시, △로 봄</t>
         </is>
       </c>
       <c r="K49" s="2"/>
@@ -2542,13 +2519,13 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|湳</t>
+          <t xml:space="preserve">㴌|–湳</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-湳</t>
+          <t xml:space="preserve">㴌
+–湳</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -2558,7 +2535,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">윗글자 淋/㴌, 아랫글자 湳/㴌 애매</t>
+          <t xml:space="preserve">아랫글자 앞 짧은 가로선(–湳)</t>
         </is>
       </c>
       <c r="K50" s="2"/>
@@ -2981,7 +2958,7 @@
       <c r="I61" s="3"/>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D 모양으로 흘린 △</t>
+          <t xml:space="preserve">D 모양으로 흘린 끝 표시, △로 봄</t>
         </is>
       </c>
       <c r="K61" s="2"/>
@@ -3085,23 +3062,27 @@
       <c r="F64" s="2">
         <v>1</v>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–|無</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="J64" s="4"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 노 위에 점</t>
+        </is>
+      </c>
       <c r="K64" s="2"/>
     </row>
     <row r="65">
@@ -3363,22 +3344,26 @@
       <c r="F71" s="2">
         <v>4</v>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J71" s="4"/>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑 왼쪽에 짧은 가로선 비슷한 획</t>
+        </is>
+      </c>
       <c r="K71" s="2"/>
     </row>
     <row r="72">
@@ -3588,23 +3573,27 @@
       <c r="F77" s="2">
         <v>2</v>
       </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|仲</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|–仲</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
+–仲</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J77" s="4"/>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲 앞 짧은 가로선(–仲)</t>
+        </is>
+      </c>
       <c r="K77" s="2"/>
     </row>
     <row r="78">
@@ -3917,7 +3906,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D 모양으로 흘린 △</t>
+          <t xml:space="preserve">D 모양으로 흘린 끝 표시, △로 봄</t>
         </is>
       </c>
       <c r="K85" s="2"/>
@@ -3952,7 +3941,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="82.06" customHeight="1">
+    <row r="2" ht="77.61" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3975,14 +3964,14 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="82.06" customHeight="1">
+    <row r="3" ht="77.61" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
@@ -3992,31 +3981,31 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
       <c r="F3" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-湳</t>
-        </is>
-      </c>
-      <c r="G3" s="30" t="inlineStr">
+          <t xml:space="preserve">㴌
+–湳</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
       <c r="H3" s="21"/>
-      <c r="I3" s="29"/>
+      <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">낮
 에</t>
@@ -4028,7 +4017,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M3" s="30" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4039,7 +4028,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="O3" s="29" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4050,26 +4039,26 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q3" s="29" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="82.06" customHeight="1">
+    <row r="4" ht="77.61" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4079,20 +4068,20 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="H4" s="21"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="23" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="K4" s="32" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">낮
 에</t>
@@ -4103,7 +4092,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M4" s="32" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
@@ -4113,7 +4102,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O4" s="31" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">녁</t>
         </is>
@@ -4123,13 +4112,13 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q4" s="31" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">침</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="82.06" customHeight="1">
+    <row r="5" ht="77.61" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4138,18 +4127,18 @@
 南</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -4159,19 +4148,19 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="33" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="H5" s="21"/>
-      <c r="I5" s="33"/>
+      <c r="I5" s="27"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K5" s="33" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4181,13 +4170,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="33"/>
+      <c r="M5" s="27"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O5" s="33" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4197,21 +4186,21 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q5" s="33" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="82.06" customHeight="1">
+    <row r="6" ht="77.61" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="C6" s="29" t="inlineStr">
+–仲</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4222,7 +4211,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
@@ -4232,20 +4221,20 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="H6" s="21"/>
-      <c r="I6" s="29"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="K6" s="29" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">밤
 에</t>
@@ -4257,7 +4246,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M6" s="29" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4268,7 +4257,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="O6" s="29" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 는</t>
@@ -4280,21 +4269,21 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q6" s="29" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 는</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="82.06" customHeight="1">
+    <row r="7" ht="77.61" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4305,7 +4294,7 @@
 無</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -4315,16 +4304,16 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="21"/>
-      <c r="I7" s="31"/>
+      <c r="I7" s="25"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K7" s="31" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">밤
 에</t>
@@ -4335,7 +4324,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M7" s="31" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4345,7 +4334,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O7" s="31" t="inlineStr">
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4355,13 +4344,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="31" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="82.06" customHeight="1">
+    <row r="8" ht="77.61" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4370,7 +4359,7 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4380,7 +4369,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -4391,15 +4380,15 @@
 △</t>
         </is>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="21"/>
-      <c r="I8" s="33"/>
+      <c r="I8" s="27"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="33" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4410,7 +4399,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M8" s="34" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">냐</t>
         </is>
@@ -4420,7 +4409,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O8" s="33" t="inlineStr">
+      <c r="O8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4431,20 +4420,20 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q8" s="33" t="inlineStr">
+      <c r="Q8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="82.06" customHeight="1">
+    <row r="9" ht="77.61" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
@@ -4455,7 +4444,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내
 가</t>
@@ -4467,20 +4456,20 @@
 㴌</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">닐</t>
         </is>
       </c>
       <c r="H9" s="21"/>
-      <c r="I9" s="29"/>
+      <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K9" s="29" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">참
 사</t>
@@ -4492,7 +4481,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M9" s="29" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">두
 리</t>
@@ -4504,7 +4493,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O9" s="29" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님
 이</t>
@@ -4516,14 +4505,14 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q9" s="29" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">배
 가</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="82.06" customHeight="1">
+    <row r="10" ht="77.61" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4532,7 +4521,7 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4543,7 +4532,7 @@
 南</t>
         </is>
       </c>
-      <c r="E10" s="31" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">돌
 아</t>
@@ -4555,32 +4544,32 @@
 湳</t>
         </is>
       </c>
-      <c r="G10" s="31" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="H10" s="21"/>
-      <c r="I10" s="31"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="32" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">랑
 이</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="M10" s="31" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
@@ -4591,7 +4580,7 @@
 南</t>
         </is>
       </c>
-      <c r="O10" s="31" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 리</t>
@@ -4603,13 +4592,13 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q10" s="32" t="inlineStr">
+      <c r="Q10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="82.06" customHeight="1">
+    <row r="11" ht="77.61" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4618,7 +4607,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4628,7 +4617,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
@@ -4638,20 +4627,20 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G11" s="33" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="H11" s="21"/>
-      <c r="I11" s="33"/>
+      <c r="I11" s="27"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="33" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -4662,7 +4651,7 @@
 湳</t>
         </is>
       </c>
-      <c r="M11" s="33" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -4673,7 +4662,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O11" s="33" t="inlineStr">
+      <c r="O11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
@@ -4684,30 +4673,30 @@
 湳</t>
         </is>
       </c>
-      <c r="Q11" s="33" t="inlineStr">
+      <c r="Q11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">파</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="82.06" customHeight="1">
+    <row r="12" ht="77.61" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4717,19 +4706,19 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="H12" s="21"/>
-      <c r="I12" s="29"/>
+      <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="29" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4739,17 +4728,17 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="29" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="N12" s="23" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="30" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -4759,42 +4748,42 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q12" s="29" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="82.06" customHeight="1">
+    <row r="13" ht="77.61" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="31"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E13" s="31"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="21"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="31" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4805,7 +4794,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="M13" s="31" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4815,7 +4804,7 @@
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="O13" s="31" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4826,13 +4815,13 @@
 㴌</t>
         </is>
       </c>
-      <c r="Q13" s="31" t="inlineStr">
+      <c r="Q13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="82.06" customHeight="1">
+    <row r="14" ht="77.61" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -4840,13 +4829,13 @@
 △</t>
         </is>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="28"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="33"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
@@ -4854,23 +4843,23 @@
 △</t>
         </is>
       </c>
-      <c r="G14" s="34"/>
+      <c r="G14" s="28"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="33"/>
+      <c r="I14" s="27"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K14" s="34"/>
+      <c r="K14" s="28"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △</t>
         </is>
       </c>
-      <c r="M14" s="33" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -4881,13 +4870,13 @@
 △</t>
         </is>
       </c>
-      <c r="O14" s="34"/>
+      <c r="O14" s="28"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q14" s="33" t="inlineStr">
+      <c r="Q14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
